--- a/regionais/registroNDI.xlsx
+++ b/regionais/registroNDI.xlsx
@@ -15100,7 +15100,7 @@
         <v>25987</v>
       </c>
       <c r="K64" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
     </row>
     <row r="65">
@@ -18685,7 +18685,7 @@
         <v>1403</v>
       </c>
       <c r="K64" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="65">
@@ -60090,7 +60090,7 @@
         <v>4226</v>
       </c>
       <c r="K64" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="65">
@@ -67260,7 +67260,7 @@
         <v>5085</v>
       </c>
       <c r="K64" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
     </row>
     <row r="65">
@@ -79750,7 +79750,7 @@
         <v>12508</v>
       </c>
       <c r="K64" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
     </row>
     <row r="65">

--- a/regionais/registroNDI.xlsx
+++ b/regionais/registroNDI.xlsx
@@ -15100,7 +15100,7 @@
         <v>25987</v>
       </c>
       <c r="K64" t="n">
-        <v>59</v>
+        <v>66</v>
       </c>
     </row>
     <row r="65">
@@ -18685,7 +18685,7 @@
         <v>1403</v>
       </c>
       <c r="K64" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="65">
@@ -21715,7 +21715,7 @@
         <v>230</v>
       </c>
       <c r="K49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -67260,7 +67260,7 @@
         <v>5085</v>
       </c>
       <c r="K64" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="65">
@@ -79750,7 +79750,7 @@
         <v>12508</v>
       </c>
       <c r="K64" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="65">

--- a/regionais/registroNDI.xlsx
+++ b/regionais/registroNDI.xlsx
@@ -15100,7 +15100,7 @@
         <v>25987</v>
       </c>
       <c r="K64" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="65">
@@ -18685,7 +18685,7 @@
         <v>1403</v>
       </c>
       <c r="K64" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="65">
@@ -60090,7 +60090,7 @@
         <v>4226</v>
       </c>
       <c r="K64" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="65">

--- a/regionais/registroNDI.xlsx
+++ b/regionais/registroNDI.xlsx
@@ -4327,7 +4327,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -7912,7 +7912,7 @@
         <v>6.092731371473832e-05</v>
       </c>
       <c r="E64" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F64" t="n">
         <v>19069</v>
@@ -11497,7 +11497,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -15082,7 +15082,7 @@
         <v>0.03779132977175335</v>
       </c>
       <c r="E64" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F64" t="n">
         <v>182431</v>
@@ -15100,7 +15100,7 @@
         <v>25987</v>
       </c>
       <c r="K64" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
     <row r="65">
@@ -18667,7 +18667,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -21697,7 +21697,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F49" t="n">
         <v>4406</v>
@@ -25134,7 +25134,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F64" t="n">
         <v>24863</v>
@@ -28164,7 +28164,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -31379,7 +31379,7 @@
         <v>0.05786350148367952</v>
       </c>
       <c r="E64" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -34964,7 +34964,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -38549,7 +38549,7 @@
         <v>0.03652520856002902</v>
       </c>
       <c r="E64" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -42134,7 +42134,7 @@
         <v>0.04941471021017724</v>
       </c>
       <c r="E64" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F64" t="n">
         <v>36442</v>
@@ -45719,7 +45719,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -49304,7 +49304,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -52889,7 +52889,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -56474,7 +56474,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -60072,7 +60072,7 @@
         <v>0.002821627392663769</v>
       </c>
       <c r="E64" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F64" t="n">
         <v>61122</v>
@@ -63657,7 +63657,7 @@
         <v>0.003638899839281924</v>
       </c>
       <c r="E64" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F64" t="n">
         <v>51839</v>
@@ -67242,7 +67242,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F64" t="n">
         <v>14529</v>
@@ -67257,7 +67257,7 @@
         <v>0</v>
       </c>
       <c r="J64" t="n">
-        <v>5085</v>
+        <v>5084</v>
       </c>
       <c r="K64" t="n">
         <v>34</v>
@@ -70272,7 +70272,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -72932,7 +72932,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -76147,7 +76147,7 @@
         <v>-9.082652134423252e-05</v>
       </c>
       <c r="E64" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -79732,7 +79732,7 @@
         <v>0.008930898193189716</v>
       </c>
       <c r="E64" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F64" t="n">
         <v>104677</v>

--- a/regionais/registroNDI.xlsx
+++ b/regionais/registroNDI.xlsx
@@ -4327,7 +4327,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -7912,7 +7912,7 @@
         <v>6.092731371473832e-05</v>
       </c>
       <c r="E64" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F64" t="n">
         <v>19069</v>
@@ -11497,7 +11497,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -15082,7 +15082,7 @@
         <v>0.03779132977175335</v>
       </c>
       <c r="E64" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F64" t="n">
         <v>182431</v>
@@ -18667,7 +18667,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -21697,7 +21697,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F49" t="n">
         <v>4406</v>
@@ -25134,7 +25134,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F64" t="n">
         <v>24863</v>
@@ -28164,7 +28164,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -31379,7 +31379,7 @@
         <v>0.05786350148367952</v>
       </c>
       <c r="E64" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -34964,7 +34964,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -38549,7 +38549,7 @@
         <v>0.03652520856002902</v>
       </c>
       <c r="E64" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -42134,7 +42134,7 @@
         <v>0.04941471021017724</v>
       </c>
       <c r="E64" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F64" t="n">
         <v>36442</v>
@@ -45719,7 +45719,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -49304,7 +49304,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -52889,7 +52889,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -56474,7 +56474,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -60072,7 +60072,7 @@
         <v>0.002821627392663769</v>
       </c>
       <c r="E64" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F64" t="n">
         <v>61122</v>
@@ -63657,7 +63657,7 @@
         <v>0.003638899839281924</v>
       </c>
       <c r="E64" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F64" t="n">
         <v>51839</v>
@@ -67242,7 +67242,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F64" t="n">
         <v>14529</v>
@@ -70272,7 +70272,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -72932,7 +72932,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -76147,7 +76147,7 @@
         <v>-9.082652134423252e-05</v>
       </c>
       <c r="E64" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -79732,7 +79732,7 @@
         <v>0.008930898193189716</v>
       </c>
       <c r="E64" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F64" t="n">
         <v>104677</v>

--- a/regionais/registroNDI.xlsx
+++ b/regionais/registroNDI.xlsx
@@ -4327,7 +4327,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -7912,7 +7912,7 @@
         <v>6.092731371473832e-05</v>
       </c>
       <c r="E64" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F64" t="n">
         <v>19069</v>
@@ -11497,7 +11497,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -15082,7 +15082,7 @@
         <v>0.03779132977175335</v>
       </c>
       <c r="E64" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F64" t="n">
         <v>182431</v>
@@ -18667,7 +18667,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -21697,7 +21697,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F49" t="n">
         <v>4406</v>
@@ -25134,7 +25134,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F64" t="n">
         <v>24863</v>
@@ -28164,7 +28164,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -31379,7 +31379,7 @@
         <v>0.05786350148367952</v>
       </c>
       <c r="E64" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -34964,7 +34964,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -38549,7 +38549,7 @@
         <v>0.03652520856002902</v>
       </c>
       <c r="E64" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -42134,7 +42134,7 @@
         <v>0.04941471021017724</v>
       </c>
       <c r="E64" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F64" t="n">
         <v>36442</v>
@@ -45719,7 +45719,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -49304,7 +49304,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -52889,7 +52889,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -56474,7 +56474,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -60072,7 +60072,7 @@
         <v>0.002821627392663769</v>
       </c>
       <c r="E64" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F64" t="n">
         <v>61122</v>
@@ -63657,7 +63657,7 @@
         <v>0.003638899839281924</v>
       </c>
       <c r="E64" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F64" t="n">
         <v>51839</v>
@@ -67242,7 +67242,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F64" t="n">
         <v>14529</v>
@@ -70272,7 +70272,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -72932,7 +72932,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -76147,7 +76147,7 @@
         <v>-9.082652134423252e-05</v>
       </c>
       <c r="E64" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -79732,7 +79732,7 @@
         <v>0.008930898193189716</v>
       </c>
       <c r="E64" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F64" t="n">
         <v>104677</v>

--- a/regionais/registroNDI.xlsx
+++ b/regionais/registroNDI.xlsx
@@ -11512,7 +11512,7 @@
         <v>0</v>
       </c>
       <c r="J64" t="n">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="K64" t="n">
         <v>1</v>

--- a/regionais/registroNDI.xlsx
+++ b/regionais/registroNDI.xlsx
@@ -39267,7 +39267,7 @@
         <v>0</v>
       </c>
       <c r="J73" t="n">
-        <v>1726</v>
+        <v>1725</v>
       </c>
       <c r="K73" t="n">
         <v>4</v>

--- a/regionais/registroNDI.xlsx
+++ b/regionais/registroNDI.xlsx
@@ -15544,7 +15544,7 @@
         <v>25987</v>
       </c>
       <c r="K73" t="n">
-        <v>70</v>
+        <v>83</v>
       </c>
     </row>
     <row r="74">
@@ -64637,7 +64637,7 @@
         <v>4580</v>
       </c>
       <c r="K73" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="74">

--- a/regionais/registroNDI.xlsx
+++ b/regionais/registroNDI.xlsx
@@ -4678,7 +4678,7 @@
         <v>1123</v>
       </c>
       <c r="K73" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="74">
@@ -64637,7 +64637,7 @@
         <v>4580</v>
       </c>
       <c r="K73" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="74">
@@ -77275,7 +77275,7 @@
         <v>788</v>
       </c>
       <c r="K73" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="74">
@@ -80897,7 +80897,7 @@
         <v>12508</v>
       </c>
       <c r="K73" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="74">

--- a/regionais/registroNDI.xlsx
+++ b/regionais/registroNDI.xlsx
@@ -25707,7 +25707,7 @@
         <v>1905</v>
       </c>
       <c r="K73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74">

--- a/regionais/registroNDI.xlsx
+++ b/regionais/registroNDI.xlsx
@@ -4660,7 +4660,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -8282,7 +8282,7 @@
         <v>0.006376456161863887</v>
       </c>
       <c r="E73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F73" t="n">
         <v>19069</v>
@@ -11904,7 +11904,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -15526,7 +15526,7 @@
         <v>0.03770107406750803</v>
       </c>
       <c r="E73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F73" t="n">
         <v>182431</v>
@@ -15544,7 +15544,7 @@
         <v>25987</v>
       </c>
       <c r="K73" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
     </row>
     <row r="74">
@@ -19148,7 +19148,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -22178,7 +22178,7 @@
         <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F57" t="n">
         <v>4406</v>
@@ -25689,7 +25689,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F73" t="n">
         <v>24863</v>
@@ -28645,7 +28645,7 @@
         <v>0</v>
       </c>
       <c r="E55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F55" t="n">
         <v>0</v>
@@ -32008,7 +32008,7 @@
         <v>0.05786350148367952</v>
       </c>
       <c r="E73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -35630,7 +35630,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -39252,7 +39252,7 @@
         <v>0.03652520856002902</v>
       </c>
       <c r="E73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -39270,7 +39270,7 @@
         <v>1725</v>
       </c>
       <c r="K73" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="74">
@@ -42874,7 +42874,7 @@
         <v>0.04941471021017724</v>
       </c>
       <c r="E73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F73" t="n">
         <v>36442</v>
@@ -42892,7 +42892,7 @@
         <v>2949</v>
       </c>
       <c r="K73" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="74">
@@ -46496,7 +46496,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -50118,7 +50118,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -53740,7 +53740,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -57362,7 +57362,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -60997,7 +60997,7 @@
         <v>0.002821627392663769</v>
       </c>
       <c r="E73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F73" t="n">
         <v>61122</v>
@@ -61015,7 +61015,7 @@
         <v>4226</v>
       </c>
       <c r="K73" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="74">
@@ -64619,7 +64619,7 @@
         <v>0.004507033704113996</v>
       </c>
       <c r="E73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F73" t="n">
         <v>51839</v>
@@ -68241,7 +68241,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F73" t="n">
         <v>14529</v>
@@ -71197,7 +71197,7 @@
         <v>0</v>
       </c>
       <c r="E55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F55" t="n">
         <v>0</v>
@@ -73894,7 +73894,7 @@
         <v>0</v>
       </c>
       <c r="E55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F55" t="n">
         <v>0</v>
@@ -77257,7 +77257,7 @@
         <v>-9.082652134423252e-05</v>
       </c>
       <c r="E73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -80879,7 +80879,7 @@
         <v>0.008930898193189716</v>
       </c>
       <c r="E73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F73" t="n">
         <v>104677</v>
@@ -80897,7 +80897,7 @@
         <v>12508</v>
       </c>
       <c r="K73" t="n">
-        <v>80</v>
+        <v>87</v>
       </c>
     </row>
     <row r="74">

--- a/regionais/registroNDI.xlsx
+++ b/regionais/registroNDI.xlsx
@@ -4660,7 +4660,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -8282,7 +8282,7 @@
         <v>0.006376456161863887</v>
       </c>
       <c r="E73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F73" t="n">
         <v>19069</v>
@@ -11904,7 +11904,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -15526,7 +15526,7 @@
         <v>0.03770107406750803</v>
       </c>
       <c r="E73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F73" t="n">
         <v>182431</v>
@@ -15544,7 +15544,7 @@
         <v>25987</v>
       </c>
       <c r="K73" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="74">
@@ -19148,7 +19148,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -22178,7 +22178,7 @@
         <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F57" t="n">
         <v>4406</v>
@@ -25689,7 +25689,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F73" t="n">
         <v>24863</v>
@@ -28645,7 +28645,7 @@
         <v>0</v>
       </c>
       <c r="E55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F55" t="n">
         <v>0</v>
@@ -32008,7 +32008,7 @@
         <v>0.05786350148367952</v>
       </c>
       <c r="E73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -35630,7 +35630,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -39252,7 +39252,7 @@
         <v>0.03652520856002902</v>
       </c>
       <c r="E73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -42874,7 +42874,7 @@
         <v>0.04941471021017724</v>
       </c>
       <c r="E73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F73" t="n">
         <v>36442</v>
@@ -46496,7 +46496,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -50118,7 +50118,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -53740,7 +53740,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -57362,7 +57362,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -60997,7 +60997,7 @@
         <v>0.002821627392663769</v>
       </c>
       <c r="E73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F73" t="n">
         <v>61122</v>
@@ -64619,7 +64619,7 @@
         <v>0.004507033704113996</v>
       </c>
       <c r="E73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F73" t="n">
         <v>51839</v>
@@ -64637,7 +64637,7 @@
         <v>4580</v>
       </c>
       <c r="K73" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="74">
@@ -68241,7 +68241,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F73" t="n">
         <v>14529</v>
@@ -71197,7 +71197,7 @@
         <v>0</v>
       </c>
       <c r="E55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F55" t="n">
         <v>0</v>
@@ -73894,7 +73894,7 @@
         <v>0</v>
       </c>
       <c r="E55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F55" t="n">
         <v>0</v>
@@ -77257,7 +77257,7 @@
         <v>-9.082652134423252e-05</v>
       </c>
       <c r="E73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -80879,7 +80879,7 @@
         <v>0.008930898193189716</v>
       </c>
       <c r="E73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F73" t="n">
         <v>104677</v>
@@ -80897,7 +80897,7 @@
         <v>12508</v>
       </c>
       <c r="K73" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
     </row>
     <row r="74">

--- a/regionais/registroNDI.xlsx
+++ b/regionais/registroNDI.xlsx
@@ -15544,7 +15544,7 @@
         <v>25987</v>
       </c>
       <c r="K73" t="n">
-        <v>88</v>
+        <v>93</v>
       </c>
     </row>
     <row r="74">
@@ -61015,7 +61015,7 @@
         <v>4226</v>
       </c>
       <c r="K73" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="74">
@@ -64637,7 +64637,7 @@
         <v>4580</v>
       </c>
       <c r="K73" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="74">
@@ -80897,7 +80897,7 @@
         <v>12508</v>
       </c>
       <c r="K73" t="n">
-        <v>90</v>
+        <v>105</v>
       </c>
     </row>
     <row r="74">

--- a/regionais/registroNDI.xlsx
+++ b/regionais/registroNDI.xlsx
@@ -15544,7 +15544,7 @@
         <v>25987</v>
       </c>
       <c r="K73" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="74">
@@ -61015,7 +61015,7 @@
         <v>4226</v>
       </c>
       <c r="K73" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="74">
@@ -68259,7 +68259,7 @@
         <v>5084</v>
       </c>
       <c r="K73" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="74">

--- a/regionais/registroNDI.xlsx
+++ b/regionais/registroNDI.xlsx
@@ -15544,7 +15544,7 @@
         <v>25987</v>
       </c>
       <c r="K73" t="n">
-        <v>95</v>
+        <v>103</v>
       </c>
     </row>
     <row r="74">
@@ -61015,7 +61015,7 @@
         <v>4226</v>
       </c>
       <c r="K73" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="74">
@@ -80897,7 +80897,7 @@
         <v>12508</v>
       </c>
       <c r="K73" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="74">

--- a/regionais/registroNDI.xlsx
+++ b/regionais/registroNDI.xlsx
@@ -15544,7 +15544,7 @@
         <v>25987</v>
       </c>
       <c r="K73" t="n">
-        <v>103</v>
+        <v>109</v>
       </c>
     </row>
     <row r="74">
@@ -46514,7 +46514,7 @@
         <v>159</v>
       </c>
       <c r="K73" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="74">
@@ -64637,7 +64637,7 @@
         <v>4580</v>
       </c>
       <c r="K73" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="74">
@@ -80870,13 +80870,13 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>185837</v>
+        <v>186413</v>
       </c>
       <c r="C73" t="n">
         <v>0</v>
       </c>
       <c r="D73" s="3" t="n">
-        <v>0.008930898193189716</v>
+        <v>0.01205806984016678</v>
       </c>
       <c r="E73" t="n">
         <v>2</v>
@@ -80897,7 +80897,7 @@
         <v>12508</v>
       </c>
       <c r="K73" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="74">
@@ -80913,7 +80913,7 @@
         <v>0</v>
       </c>
       <c r="D74" s="3" t="n">
-        <v>-0.1361031441532095</v>
+        <v>-0.1387725105008771</v>
       </c>
       <c r="E74" t="n">
         <v>1</v>

--- a/regionais/registroNDI.xlsx
+++ b/regionais/registroNDI.xlsx
@@ -15544,7 +15544,7 @@
         <v>25987</v>
       </c>
       <c r="K73" t="n">
-        <v>109</v>
+        <v>113</v>
       </c>
     </row>
     <row r="74">
@@ -39270,7 +39270,7 @@
         <v>1725</v>
       </c>
       <c r="K73" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="74">
@@ -80897,7 +80897,7 @@
         <v>12508</v>
       </c>
       <c r="K73" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="74">

--- a/regionais/registroNDI.xlsx
+++ b/regionais/registroNDI.xlsx
@@ -15544,7 +15544,7 @@
         <v>25987</v>
       </c>
       <c r="K73" t="n">
-        <v>113</v>
+        <v>116</v>
       </c>
     </row>
     <row r="74">
@@ -80897,7 +80897,7 @@
         <v>12508</v>
       </c>
       <c r="K73" t="n">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="74">

--- a/regionais/registroNDI.xlsx
+++ b/regionais/registroNDI.xlsx
@@ -8300,7 +8300,7 @@
         <v>1099</v>
       </c>
       <c r="K73" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="74">
@@ -15544,7 +15544,7 @@
         <v>25987</v>
       </c>
       <c r="K73" t="n">
-        <v>116</v>
+        <v>130</v>
       </c>
     </row>
     <row r="74">
@@ -42892,7 +42892,7 @@
         <v>2949</v>
       </c>
       <c r="K73" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="74">
@@ -61015,7 +61015,7 @@
         <v>4226</v>
       </c>
       <c r="K73" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="74">
@@ -80870,13 +80870,13 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>186413</v>
+        <v>188168</v>
       </c>
       <c r="C73" t="n">
         <v>0</v>
       </c>
       <c r="D73" s="3" t="n">
-        <v>0.01205806984016678</v>
+        <v>0.02158617095205003</v>
       </c>
       <c r="E73" t="n">
         <v>2</v>
@@ -80897,7 +80897,7 @@
         <v>12508</v>
       </c>
       <c r="K73" t="n">
-        <v>113</v>
+        <v>118</v>
       </c>
     </row>
     <row r="74">
@@ -80913,7 +80913,7 @@
         <v>0</v>
       </c>
       <c r="D74" s="3" t="n">
-        <v>-0.1387725105008771</v>
+        <v>-0.1468049827813443</v>
       </c>
       <c r="E74" t="n">
         <v>1</v>

--- a/regionais/registroNDI.xlsx
+++ b/regionais/registroNDI.xlsx
@@ -15544,7 +15544,7 @@
         <v>25987</v>
       </c>
       <c r="K73" t="n">
-        <v>130</v>
+        <v>135</v>
       </c>
     </row>
     <row r="74">
@@ -42892,7 +42892,7 @@
         <v>2949</v>
       </c>
       <c r="K73" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="74">

--- a/regionais/registroNDI.xlsx
+++ b/regionais/registroNDI.xlsx
@@ -15517,34 +15517,34 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>300813</v>
+        <v>301951</v>
       </c>
       <c r="C73" t="n">
         <v>9415</v>
       </c>
       <c r="D73" s="3" t="n">
-        <v>0.03770107406750803</v>
+        <v>0.0415076415671819</v>
       </c>
       <c r="E73" t="n">
         <v>2</v>
       </c>
       <c r="F73" t="n">
-        <v>182431</v>
+        <v>193622</v>
       </c>
       <c r="G73" t="n">
         <v>4726</v>
       </c>
       <c r="H73" t="n">
-        <v>40017</v>
+        <v>66098</v>
       </c>
       <c r="I73" s="3" t="n">
-        <v>0.2161349036402569</v>
+        <v>0.4156638115631692</v>
       </c>
       <c r="J73" t="n">
         <v>25987</v>
       </c>
       <c r="K73" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="74">
@@ -15560,7 +15560,7 @@
         <v>0</v>
       </c>
       <c r="D74" s="3" t="n">
-        <v>-0.1233060845571644</v>
+        <v>-0.1265102805058998</v>
       </c>
       <c r="E74" t="n">
         <v>1</v>
@@ -15575,7 +15575,7 @@
         <v>0</v>
       </c>
       <c r="I74" s="3" t="n">
-        <v>-0.2852879290763908</v>
+        <v>-0.3860220990296696</v>
       </c>
       <c r="J74" t="n">
         <v>18825</v>
@@ -61015,7 +61015,7 @@
         <v>4226</v>
       </c>
       <c r="K73" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="74">
@@ -64637,7 +64637,7 @@
         <v>4580</v>
       </c>
       <c r="K73" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="74">
@@ -68259,7 +68259,7 @@
         <v>5084</v>
       </c>
       <c r="K73" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="74">

--- a/regionais/registroNDI.xlsx
+++ b/regionais/registroNDI.xlsx
@@ -15544,7 +15544,7 @@
         <v>25987</v>
       </c>
       <c r="K73" t="n">
-        <v>136</v>
+        <v>140</v>
       </c>
     </row>
     <row r="74">
@@ -19166,7 +19166,7 @@
         <v>1403</v>
       </c>
       <c r="K73" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="74">
@@ -68259,7 +68259,7 @@
         <v>5084</v>
       </c>
       <c r="K73" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
     </row>
     <row r="74">
@@ -80897,7 +80897,7 @@
         <v>12508</v>
       </c>
       <c r="K73" t="n">
-        <v>118</v>
+        <v>123</v>
       </c>
     </row>
     <row r="74">

--- a/regionais/registroNDI.xlsx
+++ b/regionais/registroNDI.xlsx
@@ -15529,7 +15529,7 @@
         <v>2</v>
       </c>
       <c r="F73" t="n">
-        <v>193622</v>
+        <v>194272</v>
       </c>
       <c r="G73" t="n">
         <v>4726</v>
@@ -15538,13 +15538,13 @@
         <v>66098</v>
       </c>
       <c r="I73" s="3" t="n">
-        <v>0.4156638115631692</v>
+        <v>0.4191434689507494</v>
       </c>
       <c r="J73" t="n">
         <v>25987</v>
       </c>
       <c r="K73" t="n">
-        <v>140</v>
+        <v>144</v>
       </c>
     </row>
     <row r="74">
@@ -15575,7 +15575,7 @@
         <v>0</v>
       </c>
       <c r="I74" s="3" t="n">
-        <v>-0.3860220990296696</v>
+        <v>-0.3875275371940731</v>
       </c>
       <c r="J74" t="n">
         <v>18825</v>
@@ -64637,7 +64637,7 @@
         <v>4580</v>
       </c>
       <c r="K73" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="74">
@@ -68259,7 +68259,7 @@
         <v>5084</v>
       </c>
       <c r="K73" t="n">
-        <v>45</v>
+        <v>52</v>
       </c>
     </row>
     <row r="74">
@@ -80897,7 +80897,7 @@
         <v>12508</v>
       </c>
       <c r="K73" t="n">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="74">

--- a/regionais/registroNDI.xlsx
+++ b/regionais/registroNDI.xlsx
@@ -15541,10 +15541,10 @@
         <v>0.4191434689507494</v>
       </c>
       <c r="J73" t="n">
-        <v>25987</v>
+        <v>25986</v>
       </c>
       <c r="K73" t="n">
-        <v>144</v>
+        <v>149</v>
       </c>
     </row>
     <row r="74">
@@ -22169,13 +22169,13 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>5292</v>
+        <v>6145</v>
       </c>
       <c r="C57" t="n">
         <v>0</v>
       </c>
       <c r="D57" s="3" t="n">
-        <v>0</v>
+        <v>0.1611866969009826</v>
       </c>
       <c r="E57" t="n">
         <v>2</v>
@@ -61015,7 +61015,7 @@
         <v>4226</v>
       </c>
       <c r="K73" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="74">
@@ -80897,7 +80897,7 @@
         <v>12508</v>
       </c>
       <c r="K73" t="n">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="74">

--- a/regionais/registroNDI.xlsx
+++ b/regionais/registroNDI.xlsx
@@ -4660,7 +4660,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -8282,7 +8282,7 @@
         <v>0.006376456161863887</v>
       </c>
       <c r="E73" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F73" t="n">
         <v>19069</v>
@@ -11904,7 +11904,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -15526,7 +15526,7 @@
         <v>0.0415076415671819</v>
       </c>
       <c r="E73" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F73" t="n">
         <v>194272</v>
@@ -19148,7 +19148,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -22178,7 +22178,7 @@
         <v>0.1611866969009826</v>
       </c>
       <c r="E57" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F57" t="n">
         <v>4406</v>
@@ -25689,7 +25689,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F73" t="n">
         <v>24863</v>
@@ -28645,7 +28645,7 @@
         <v>0</v>
       </c>
       <c r="E55" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F55" t="n">
         <v>0</v>
@@ -32008,7 +32008,7 @@
         <v>0.05786350148367952</v>
       </c>
       <c r="E73" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -35630,7 +35630,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -39252,7 +39252,7 @@
         <v>0.03652520856002902</v>
       </c>
       <c r="E73" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -42874,7 +42874,7 @@
         <v>0.04941471021017724</v>
       </c>
       <c r="E73" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F73" t="n">
         <v>36442</v>
@@ -46496,7 +46496,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -50118,7 +50118,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -53740,7 +53740,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -57362,7 +57362,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -60997,7 +60997,7 @@
         <v>0.002821627392663769</v>
       </c>
       <c r="E73" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F73" t="n">
         <v>61122</v>
@@ -64619,7 +64619,7 @@
         <v>0.004507033704113996</v>
       </c>
       <c r="E73" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F73" t="n">
         <v>51839</v>
@@ -68241,7 +68241,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F73" t="n">
         <v>14529</v>
@@ -71197,7 +71197,7 @@
         <v>0</v>
       </c>
       <c r="E55" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F55" t="n">
         <v>0</v>
@@ -73894,7 +73894,7 @@
         <v>0</v>
       </c>
       <c r="E55" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F55" t="n">
         <v>0</v>
@@ -77257,7 +77257,7 @@
         <v>-9.082652134423252e-05</v>
       </c>
       <c r="E73" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -80879,7 +80879,7 @@
         <v>0.02158617095205003</v>
       </c>
       <c r="E73" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F73" t="n">
         <v>104677</v>

--- a/regionais/registroNDI.xlsx
+++ b/regionais/registroNDI.xlsx
@@ -15517,13 +15517,13 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>301951</v>
+        <v>301978</v>
       </c>
       <c r="C73" t="n">
         <v>9415</v>
       </c>
       <c r="D73" s="3" t="n">
-        <v>0.0415076415671819</v>
+        <v>0.04159795555882619</v>
       </c>
       <c r="E73" t="n">
         <v>3</v>
@@ -15560,7 +15560,7 @@
         <v>0</v>
       </c>
       <c r="D74" s="3" t="n">
-        <v>-0.1265102805058998</v>
+        <v>-0.1265860183112658</v>
       </c>
       <c r="E74" t="n">
         <v>1</v>

--- a/regionais/registroNDI.xlsx
+++ b/regionais/registroNDI.xlsx
@@ -15988,7 +15988,7 @@
         <v>25986</v>
       </c>
       <c r="K82" t="n">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="83">
@@ -22677,7 +22677,7 @@
         <v>230</v>
       </c>
       <c r="K65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -65599,7 +65599,7 @@
         <v>4580</v>
       </c>
       <c r="K82" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="83">
@@ -69258,7 +69258,7 @@
         <v>5084</v>
       </c>
       <c r="K82" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="83">
@@ -82044,7 +82044,7 @@
         <v>12508</v>
       </c>
       <c r="K82" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="83">

--- a/regionais/registroNDI.xlsx
+++ b/regionais/registroNDI.xlsx
@@ -15988,7 +15988,7 @@
         <v>25986</v>
       </c>
       <c r="K82" t="n">
-        <v>151</v>
+        <v>157</v>
       </c>
     </row>
     <row r="83">
@@ -26262,7 +26262,7 @@
         <v>1905</v>
       </c>
       <c r="K82" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="83">

--- a/regionais/registroNDI.xlsx
+++ b/regionais/registroNDI.xlsx
@@ -4993,7 +4993,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -8652,7 +8652,7 @@
         <v>0.006376456161863887</v>
       </c>
       <c r="E82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F82" t="n">
         <v>19069</v>
@@ -12311,7 +12311,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -15970,7 +15970,7 @@
         <v>0.04039384837438983</v>
       </c>
       <c r="E82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F82" t="n">
         <v>194272</v>
@@ -19629,7 +19629,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -22659,7 +22659,7 @@
         <v>0.1611866969009826</v>
       </c>
       <c r="E65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F65" t="n">
         <v>4406</v>
@@ -26244,7 +26244,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F82" t="n">
         <v>24863</v>
@@ -29126,7 +29126,7 @@
         <v>0</v>
       </c>
       <c r="E61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F61" t="n">
         <v>0</v>
@@ -32637,7 +32637,7 @@
         <v>0.05786350148367952</v>
       </c>
       <c r="E82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -36296,7 +36296,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -39955,7 +39955,7 @@
         <v>0.03652520856002902</v>
       </c>
       <c r="E82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -43614,7 +43614,7 @@
         <v>0.04941471021017724</v>
       </c>
       <c r="E82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F82" t="n">
         <v>36442</v>
@@ -47273,7 +47273,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -50932,7 +50932,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -54591,7 +54591,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -58250,7 +58250,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -61922,7 +61922,7 @@
         <v>0.002821627392663769</v>
       </c>
       <c r="E82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F82" t="n">
         <v>61122</v>
@@ -65581,7 +65581,7 @@
         <v>0.004507033704113996</v>
       </c>
       <c r="E82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F82" t="n">
         <v>51839</v>
@@ -65599,7 +65599,7 @@
         <v>4580</v>
       </c>
       <c r="K82" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="83">
@@ -69240,7 +69240,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F82" t="n">
         <v>14529</v>
@@ -72122,7 +72122,7 @@
         <v>0</v>
       </c>
       <c r="E61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F61" t="n">
         <v>0</v>
@@ -74856,7 +74856,7 @@
         <v>0</v>
       </c>
       <c r="E61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F61" t="n">
         <v>0</v>
@@ -78367,7 +78367,7 @@
         <v>-9.082652134423252e-05</v>
       </c>
       <c r="E82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -82026,7 +82026,7 @@
         <v>0.02158617095205003</v>
       </c>
       <c r="E82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F82" t="n">
         <v>104677</v>
@@ -82044,7 +82044,7 @@
         <v>12508</v>
       </c>
       <c r="K82" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="83">

--- a/regionais/registroNDI.xlsx
+++ b/regionais/registroNDI.xlsx
@@ -5011,7 +5011,7 @@
         <v>1123</v>
       </c>
       <c r="K82" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="83">
@@ -43632,7 +43632,7 @@
         <v>2949</v>
       </c>
       <c r="K82" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="83">

--- a/regionais/registroNDI.xlsx
+++ b/regionais/registroNDI.xlsx
@@ -15988,7 +15988,7 @@
         <v>25986</v>
       </c>
       <c r="K82" t="n">
-        <v>157</v>
+        <v>161</v>
       </c>
     </row>
     <row r="83">
@@ -39973,7 +39973,7 @@
         <v>1725</v>
       </c>
       <c r="K82" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="83">
@@ -61940,7 +61940,7 @@
         <v>4226</v>
       </c>
       <c r="K82" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="83">
@@ -82044,7 +82044,7 @@
         <v>12508</v>
       </c>
       <c r="K82" t="n">
-        <v>133</v>
+        <v>140</v>
       </c>
     </row>
     <row r="83">

--- a/regionais/registroNDI.xlsx
+++ b/regionais/registroNDI.xlsx
@@ -15988,7 +15988,7 @@
         <v>25986</v>
       </c>
       <c r="K82" t="n">
-        <v>161</v>
+        <v>166</v>
       </c>
     </row>
     <row r="83">
@@ -65599,7 +65599,7 @@
         <v>4580</v>
       </c>
       <c r="K82" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="83">
@@ -82044,7 +82044,7 @@
         <v>12508</v>
       </c>
       <c r="K82" t="n">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="83">

--- a/regionais/registroNDI.xlsx
+++ b/regionais/registroNDI.xlsx
@@ -15988,7 +15988,7 @@
         <v>25986</v>
       </c>
       <c r="K82" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="83">
@@ -82044,7 +82044,7 @@
         <v>12508</v>
       </c>
       <c r="K82" t="n">
-        <v>142</v>
+        <v>147</v>
       </c>
     </row>
     <row r="83">

--- a/regionais/registroNDI.xlsx
+++ b/regionais/registroNDI.xlsx
@@ -15988,7 +15988,7 @@
         <v>25986</v>
       </c>
       <c r="K82" t="n">
-        <v>167</v>
+        <v>170</v>
       </c>
     </row>
     <row r="83">
@@ -69258,7 +69258,7 @@
         <v>5084</v>
       </c>
       <c r="K82" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="83">
@@ -82044,7 +82044,7 @@
         <v>12508</v>
       </c>
       <c r="K82" t="n">
-        <v>147</v>
+        <v>150</v>
       </c>
     </row>
     <row r="83">

--- a/regionais/registroNDI.xlsx
+++ b/regionais/registroNDI.xlsx
@@ -15988,7 +15988,7 @@
         <v>25986</v>
       </c>
       <c r="K82" t="n">
-        <v>170</v>
+        <v>174</v>
       </c>
     </row>
     <row r="83">
@@ -65599,7 +65599,7 @@
         <v>4580</v>
       </c>
       <c r="K82" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="83">
@@ -82044,7 +82044,7 @@
         <v>12508</v>
       </c>
       <c r="K82" t="n">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="83">

--- a/regionais/registroNDI.xlsx
+++ b/regionais/registroNDI.xlsx
@@ -15988,7 +15988,7 @@
         <v>25986</v>
       </c>
       <c r="K82" t="n">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="83">
@@ -39973,7 +39973,7 @@
         <v>1725</v>
       </c>
       <c r="K82" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="83">
@@ -65599,7 +65599,7 @@
         <v>4580</v>
       </c>
       <c r="K82" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="83">
@@ -82044,7 +82044,7 @@
         <v>12508</v>
       </c>
       <c r="K82" t="n">
-        <v>152</v>
+        <v>155</v>
       </c>
     </row>
     <row r="83">

--- a/regionais/registroNDI.xlsx
+++ b/regionais/registroNDI.xlsx
@@ -15988,7 +15988,7 @@
         <v>25986</v>
       </c>
       <c r="K82" t="n">
-        <v>176</v>
+        <v>182</v>
       </c>
     </row>
     <row r="83">
@@ -61931,10 +61931,10 @@
         <v>0</v>
       </c>
       <c r="H82" t="n">
-        <v>4766</v>
+        <v>6571</v>
       </c>
       <c r="I82" s="3" t="n">
-        <v>0.06978405585322292</v>
+        <v>0.09909076148725443</v>
       </c>
       <c r="J82" t="n">
         <v>4226</v>
@@ -61971,7 +61971,7 @@
         <v>0</v>
       </c>
       <c r="I83" s="3" t="n">
-        <v>-0.7241379310344828</v>
+        <v>-0.7314936551785266</v>
       </c>
       <c r="J83" t="n">
         <v>2492</v>
@@ -65599,7 +65599,7 @@
         <v>4580</v>
       </c>
       <c r="K82" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="83">
@@ -82044,7 +82044,7 @@
         <v>12508</v>
       </c>
       <c r="K82" t="n">
-        <v>155</v>
+        <v>158</v>
       </c>
     </row>
     <row r="83">

--- a/regionais/registroNDI.xlsx
+++ b/regionais/registroNDI.xlsx
@@ -43632,7 +43632,7 @@
         <v>2949</v>
       </c>
       <c r="K82" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="83">

--- a/regionais/registroNDI.xlsx
+++ b/regionais/registroNDI.xlsx
@@ -8670,7 +8670,7 @@
         <v>1099</v>
       </c>
       <c r="K82" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="83">
@@ -15988,7 +15988,7 @@
         <v>25986</v>
       </c>
       <c r="K82" t="n">
-        <v>182</v>
+        <v>186</v>
       </c>
     </row>
     <row r="83">
@@ -43632,7 +43632,7 @@
         <v>2949</v>
       </c>
       <c r="K82" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="83">
@@ -65599,7 +65599,7 @@
         <v>4580</v>
       </c>
       <c r="K82" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="83">
@@ -82044,7 +82044,7 @@
         <v>12508</v>
       </c>
       <c r="K82" t="n">
-        <v>158</v>
+        <v>166</v>
       </c>
     </row>
     <row r="83">

--- a/regionais/registroNDI.xlsx
+++ b/regionais/registroNDI.xlsx
@@ -4993,7 +4993,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -8652,7 +8652,7 @@
         <v>0.006376456161863887</v>
       </c>
       <c r="E82" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F82" t="n">
         <v>19069</v>
@@ -12311,7 +12311,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -15970,7 +15970,7 @@
         <v>0.04039384837438983</v>
       </c>
       <c r="E82" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F82" t="n">
         <v>194272</v>
@@ -15988,7 +15988,7 @@
         <v>25986</v>
       </c>
       <c r="K82" t="n">
-        <v>186</v>
+        <v>189</v>
       </c>
     </row>
     <row r="83">
@@ -19629,7 +19629,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -22659,7 +22659,7 @@
         <v>0.1611866969009826</v>
       </c>
       <c r="E65" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F65" t="n">
         <v>4406</v>
@@ -26244,7 +26244,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F82" t="n">
         <v>24863</v>
@@ -29126,7 +29126,7 @@
         <v>0</v>
       </c>
       <c r="E61" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F61" t="n">
         <v>0</v>
@@ -32637,7 +32637,7 @@
         <v>0.05786350148367952</v>
       </c>
       <c r="E82" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -36296,7 +36296,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -39955,7 +39955,7 @@
         <v>0.03652520856002902</v>
       </c>
       <c r="E82" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -43614,7 +43614,7 @@
         <v>0.04941471021017724</v>
       </c>
       <c r="E82" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F82" t="n">
         <v>36442</v>
@@ -47273,7 +47273,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -50932,7 +50932,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -54591,7 +54591,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -58250,7 +58250,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -61922,7 +61922,7 @@
         <v>0.002821627392663769</v>
       </c>
       <c r="E82" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F82" t="n">
         <v>61122</v>
@@ -65581,7 +65581,7 @@
         <v>0.004507033704113996</v>
       </c>
       <c r="E82" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F82" t="n">
         <v>51839</v>
@@ -69240,7 +69240,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F82" t="n">
         <v>14529</v>
@@ -72122,7 +72122,7 @@
         <v>0</v>
       </c>
       <c r="E61" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F61" t="n">
         <v>0</v>
@@ -74856,7 +74856,7 @@
         <v>0</v>
       </c>
       <c r="E61" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F61" t="n">
         <v>0</v>
@@ -78367,7 +78367,7 @@
         <v>-9.082652134423252e-05</v>
       </c>
       <c r="E82" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -82026,7 +82026,7 @@
         <v>0.02158617095205003</v>
       </c>
       <c r="E82" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F82" t="n">
         <v>104677</v>

--- a/regionais/registroNDI.xlsx
+++ b/regionais/registroNDI.xlsx
@@ -4993,7 +4993,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -8652,7 +8652,7 @@
         <v>0.006376456161863887</v>
       </c>
       <c r="E82" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F82" t="n">
         <v>19069</v>
@@ -12311,7 +12311,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -15970,7 +15970,7 @@
         <v>0.04039384837438983</v>
       </c>
       <c r="E82" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F82" t="n">
         <v>194272</v>
@@ -15988,7 +15988,7 @@
         <v>25986</v>
       </c>
       <c r="K82" t="n">
-        <v>189</v>
+        <v>198</v>
       </c>
     </row>
     <row r="83">
@@ -19629,7 +19629,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -22659,7 +22659,7 @@
         <v>0.1611866969009826</v>
       </c>
       <c r="E65" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F65" t="n">
         <v>4406</v>
@@ -26244,7 +26244,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F82" t="n">
         <v>24863</v>
@@ -29126,7 +29126,7 @@
         <v>0</v>
       </c>
       <c r="E61" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F61" t="n">
         <v>0</v>
@@ -32637,7 +32637,7 @@
         <v>0.05786350148367952</v>
       </c>
       <c r="E82" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -36296,7 +36296,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -39955,7 +39955,7 @@
         <v>0.03652520856002902</v>
       </c>
       <c r="E82" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -43614,7 +43614,7 @@
         <v>0.04941471021017724</v>
       </c>
       <c r="E82" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F82" t="n">
         <v>36442</v>
@@ -47273,7 +47273,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -50932,7 +50932,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -54591,7 +54591,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -58250,7 +58250,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -61922,7 +61922,7 @@
         <v>0.002821627392663769</v>
       </c>
       <c r="E82" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F82" t="n">
         <v>61122</v>
@@ -65581,7 +65581,7 @@
         <v>0.004507033704113996</v>
       </c>
       <c r="E82" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F82" t="n">
         <v>51839</v>
@@ -69240,7 +69240,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F82" t="n">
         <v>14529</v>
@@ -72122,7 +72122,7 @@
         <v>0</v>
       </c>
       <c r="E61" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F61" t="n">
         <v>0</v>
@@ -74856,7 +74856,7 @@
         <v>0</v>
       </c>
       <c r="E61" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F61" t="n">
         <v>0</v>
@@ -78367,7 +78367,7 @@
         <v>-9.082652134423252e-05</v>
       </c>
       <c r="E82" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -82026,7 +82026,7 @@
         <v>0.02158617095205003</v>
       </c>
       <c r="E82" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F82" t="n">
         <v>104677</v>

--- a/regionais/registroNDI.xlsx
+++ b/regionais/registroNDI.xlsx
@@ -15988,7 +15988,7 @@
         <v>25986</v>
       </c>
       <c r="K82" t="n">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="83">
@@ -69258,7 +69258,7 @@
         <v>5084</v>
       </c>
       <c r="K82" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="83">
@@ -82044,7 +82044,7 @@
         <v>12508</v>
       </c>
       <c r="K82" t="n">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="83">

--- a/regionais/registroNDI.xlsx
+++ b/regionais/registroNDI.xlsx
@@ -82044,7 +82044,7 @@
         <v>12508</v>
       </c>
       <c r="K82" t="n">
-        <v>168</v>
+        <v>171</v>
       </c>
     </row>
     <row r="83">

--- a/regionais/registroNDI.xlsx
+++ b/regionais/registroNDI.xlsx
@@ -15988,7 +15988,7 @@
         <v>25986</v>
       </c>
       <c r="K82" t="n">
-        <v>200</v>
+        <v>208</v>
       </c>
     </row>
     <row r="83">
@@ -19647,7 +19647,7 @@
         <v>1403</v>
       </c>
       <c r="K82" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="83">
@@ -69258,7 +69258,7 @@
         <v>5084</v>
       </c>
       <c r="K82" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="83">
@@ -82041,10 +82041,10 @@
         <v>0.07898630884824802</v>
       </c>
       <c r="J82" t="n">
-        <v>12508</v>
+        <v>12551</v>
       </c>
       <c r="K82" t="n">
-        <v>171</v>
+        <v>131</v>
       </c>
     </row>
     <row r="83">

--- a/regionais/registroNDI.xlsx
+++ b/regionais/registroNDI.xlsx
@@ -19647,7 +19647,7 @@
         <v>1403</v>
       </c>
       <c r="K82" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="83">
@@ -82044,7 +82044,7 @@
         <v>12551</v>
       </c>
       <c r="K82" t="n">
-        <v>131</v>
+        <v>134</v>
       </c>
     </row>
     <row r="83">

--- a/regionais/registroNDI.xlsx
+++ b/regionais/registroNDI.xlsx
@@ -15988,7 +15988,7 @@
         <v>25986</v>
       </c>
       <c r="K82" t="n">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="83">

--- a/regionais/registroNDI.xlsx
+++ b/regionais/registroNDI.xlsx
@@ -4993,7 +4993,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -8652,7 +8652,7 @@
         <v>0.006376456161863887</v>
       </c>
       <c r="E82" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F82" t="n">
         <v>19069</v>
@@ -12311,7 +12311,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -15970,7 +15970,7 @@
         <v>0.04039384837438983</v>
       </c>
       <c r="E82" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F82" t="n">
         <v>194272</v>
@@ -19629,7 +19629,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -22659,7 +22659,7 @@
         <v>0.1611866969009826</v>
       </c>
       <c r="E65" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F65" t="n">
         <v>4406</v>
@@ -26244,7 +26244,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F82" t="n">
         <v>24863</v>
@@ -29126,7 +29126,7 @@
         <v>0</v>
       </c>
       <c r="E61" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F61" t="n">
         <v>0</v>
@@ -32637,7 +32637,7 @@
         <v>0.05786350148367952</v>
       </c>
       <c r="E82" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -36296,7 +36296,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -39955,7 +39955,7 @@
         <v>0.03652520856002902</v>
       </c>
       <c r="E82" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -43614,7 +43614,7 @@
         <v>0.04941471021017724</v>
       </c>
       <c r="E82" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F82" t="n">
         <v>36442</v>
@@ -47273,7 +47273,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -50932,7 +50932,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -54591,7 +54591,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -58250,7 +58250,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -61922,7 +61922,7 @@
         <v>0.002821627392663769</v>
       </c>
       <c r="E82" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F82" t="n">
         <v>61122</v>
@@ -65581,7 +65581,7 @@
         <v>0.004507033704113996</v>
       </c>
       <c r="E82" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F82" t="n">
         <v>51839</v>
@@ -69240,7 +69240,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F82" t="n">
         <v>14529</v>
@@ -72122,7 +72122,7 @@
         <v>0</v>
       </c>
       <c r="E61" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F61" t="n">
         <v>0</v>
@@ -74856,7 +74856,7 @@
         <v>0</v>
       </c>
       <c r="E61" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F61" t="n">
         <v>0</v>
@@ -78367,7 +78367,7 @@
         <v>-9.082652134423252e-05</v>
       </c>
       <c r="E82" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -82026,7 +82026,7 @@
         <v>0.02158617095205003</v>
       </c>
       <c r="E82" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F82" t="n">
         <v>104677</v>

--- a/regionais/registroNDI.xlsx
+++ b/regionais/registroNDI.xlsx
@@ -4993,7 +4993,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -8652,7 +8652,7 @@
         <v>0.006376456161863887</v>
       </c>
       <c r="E82" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F82" t="n">
         <v>19069</v>
@@ -12311,7 +12311,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -15970,7 +15970,7 @@
         <v>0.04039384837438983</v>
       </c>
       <c r="E82" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F82" t="n">
         <v>194272</v>
@@ -19629,7 +19629,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -22659,7 +22659,7 @@
         <v>0.1611866969009826</v>
       </c>
       <c r="E65" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F65" t="n">
         <v>4406</v>
@@ -26244,7 +26244,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F82" t="n">
         <v>24863</v>
@@ -29126,7 +29126,7 @@
         <v>0</v>
       </c>
       <c r="E61" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F61" t="n">
         <v>0</v>
@@ -32637,7 +32637,7 @@
         <v>0.05786350148367952</v>
       </c>
       <c r="E82" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -36296,7 +36296,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -39955,7 +39955,7 @@
         <v>0.03652520856002902</v>
       </c>
       <c r="E82" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -43614,7 +43614,7 @@
         <v>0.04941471021017724</v>
       </c>
       <c r="E82" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F82" t="n">
         <v>36442</v>
@@ -47273,7 +47273,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -50932,7 +50932,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -54591,7 +54591,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -58250,7 +58250,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -61922,7 +61922,7 @@
         <v>0.002821627392663769</v>
       </c>
       <c r="E82" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F82" t="n">
         <v>61122</v>
@@ -65581,7 +65581,7 @@
         <v>0.004507033704113996</v>
       </c>
       <c r="E82" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F82" t="n">
         <v>51839</v>
@@ -69240,7 +69240,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F82" t="n">
         <v>14529</v>
@@ -72122,7 +72122,7 @@
         <v>0</v>
       </c>
       <c r="E61" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F61" t="n">
         <v>0</v>
@@ -74856,7 +74856,7 @@
         <v>0</v>
       </c>
       <c r="E61" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F61" t="n">
         <v>0</v>
@@ -78367,7 +78367,7 @@
         <v>-9.082652134423252e-05</v>
       </c>
       <c r="E82" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -82026,7 +82026,7 @@
         <v>0.02158617095205003</v>
       </c>
       <c r="E82" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F82" t="n">
         <v>104677</v>

--- a/regionais/registroNDI.xlsx
+++ b/regionais/registroNDI.xlsx
@@ -82041,7 +82041,7 @@
         <v>0.07898630884824802</v>
       </c>
       <c r="J82" t="n">
-        <v>12551</v>
+        <v>12550</v>
       </c>
       <c r="K82" t="n">
         <v>134</v>
